--- a/0179_Intercuenca_Ramis/_raw_reportes_xlsx/IDConfig_64912_completo.xlsx
+++ b/0179_Intercuenca_Ramis/_raw_reportes_xlsx/IDConfig_64912_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R797ce4410d0d429b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R7a38af14095f462f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.9055</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1262</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.2194</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.2710</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.3136</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.4844</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.2484</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.1205</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     10.7203</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/0179_Intercuenca_Ramis/_raw_reportes_xlsx/IDConfig_64912_completo.xlsx
+++ b/0179_Intercuenca_Ramis/_raw_reportes_xlsx/IDConfig_64912_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R7a38af14095f462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb4b321aea6fb4f84"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3626</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3311</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6454</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7883</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.3970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8267</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0331</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.3478</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.5085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.5830</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.4446</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8792</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.4737</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0675</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.1011</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.0836</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.3833</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      6.8450</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0564</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3259</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7268</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5576</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5013</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0895</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.2980</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.3369</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0758</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6731</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.6191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8485</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7393</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5149</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2058</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2273</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4047</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.8961</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5751</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      9.1734</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7784</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4849</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5624</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
